--- a/7rmartSupermarket_Project/src/test/resources/TestData_7martProject.xlsx
+++ b/7rmartSupermarket_Project/src/test/resources/TestData_7martProject.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEVIKA\eclipse-workspace\7rmartSupermarket_Project\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEVIKA\git\SeleniumProject_7rmartSupermarket\7rmartSupermarket_Project\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B613843-2236-4E78-9948-0550B1FE3087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5701C7-86CD-471A-9BFE-7F584660F295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="970" yWindow="1980" windowWidth="14400" windowHeight="8170" firstSheet="3" activeTab="5" xr2:uid="{9B576C8B-8DBA-4970-BEF7-B33DF54F96B0}"/>
+    <workbookView xWindow="970" yWindow="1980" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{9B576C8B-8DBA-4970-BEF7-B33DF54F96B0}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="adminusers" sheetId="3" r:id="rId3"/>
     <sheet name="footertext" sheetId="4" r:id="rId4"/>
     <sheet name="contactpage" sheetId="5" r:id="rId5"/>
-    <sheet name="categorypage" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>username</t>
   </si>
@@ -60,15 +59,9 @@
     <t>news</t>
   </si>
   <si>
-    <t>New Product Launched!!</t>
-  </si>
-  <si>
     <t>usertype</t>
   </si>
   <si>
-    <t>Dev_Admin</t>
-  </si>
-  <si>
     <t>devpassword</t>
   </si>
   <si>
@@ -99,10 +92,10 @@
     <t>JNB132 Marine Way</t>
   </si>
   <si>
-    <t>categoryname</t>
-  </si>
-  <si>
-    <t>Egg</t>
+    <t>[gets from faker class]</t>
+  </si>
+  <si>
+    <t>New Categories Added!!</t>
   </si>
 </sst>
 </file>
@@ -547,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -559,6 +552,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DFF1AE4-9010-4CD2-BB0B-81CA3DD3FEC6}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -568,15 +565,15 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -599,21 +596,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>1273888933</v>
@@ -642,19 +639,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -662,10 +659,10 @@
         <v>2324447588</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -680,27 +677,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EFB9FB-A704-4E87-8188-C42F3CB0FA6A}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>